--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589F1FAB-4E70-4960-B6B7-C8A411E27860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD2E31A-621E-458F-8D94-D5CC2B6E3146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,9 +253,6 @@
   </si>
   <si>
     <t>No regular classes. Studied at home and relaxed.</t>
-  </si>
-  <si>
-    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1714,7 +1711,7 @@
         <v>490</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>63</v>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD2E31A-621E-458F-8D94-D5CC2B6E3146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5975F64-7E91-4D11-BC90-48E5E3ED1E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>No regular classes. Studied at home and relaxed.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1711,7 +1714,7 @@
         <v>490</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>63</v>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5975F64-7E91-4D11-BC90-48E5E3ED1E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3E2266-7DD7-44AC-B0BB-F01750E37AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,9 +253,6 @@
   </si>
   <si>
     <t>No regular classes. Studied at home and relaxed.</t>
-  </si>
-  <si>
-    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1714,7 +1711,7 @@
         <v>490</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>63</v>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3E2266-7DD7-44AC-B0BB-F01750E37AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22EE2D0-5B42-4EB7-9AE7-1245D5AACA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>No regular classes. Studied at home and relaxed.</t>
+  </si>
+  <si>
+    <t>Completed daily tasks and some exercise.</t>
   </si>
 </sst>
 </file>
@@ -1723,27 +1726,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="14">
+        <v>360</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>680</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22EE2D0-5B42-4EB7-9AE7-1245D5AACA97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB90B1B-659D-40C5-9C7E-BCB4D5277253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>Completed daily tasks and some exercise.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -1772,93 +1775,189 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>200</v>
+      </c>
+      <c r="G22" s="14">
+        <v>4</v>
+      </c>
+      <c r="H22" s="14">
+        <v>60</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>60</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>240</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>45</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>585</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>45</v>
+      </c>
+      <c r="F25" s="14">
+        <v>150</v>
+      </c>
+      <c r="G25" s="14">
+        <v>3</v>
+      </c>
+      <c r="H25" s="14">
+        <v>45</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB90B1B-659D-40C5-9C7E-BCB4D5277253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D61ACB2-9204-4365-B7B1-A513521946BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>Classes were a little tiring and did some revision after coming home.</t>
   </si>
 </sst>
 </file>
@@ -1959,49 +1962,97 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>180</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>180</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D61ACB2-9204-4365-B7B1-A513521946BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB96C08-41DE-4606-A0B5-398947B0D4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Classes were a little tiring and did some revision after coming home.</t>
+  </si>
+  <si>
+    <t>Had regular classes and preparing for CA1 at home.</t>
   </si>
 </sst>
 </file>
@@ -1881,7 +1884,7 @@
         <v>60</v>
       </c>
       <c r="D24" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="E24" s="14">
         <v>30</v>
@@ -1897,11 +1900,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>795</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>645</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>49</v>
@@ -2054,49 +2057,97 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>45</v>
+      </c>
+      <c r="D28" s="14">
+        <v>240</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>300</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>315</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>45</v>
+      </c>
+      <c r="D29" s="14">
+        <v>180</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>875</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>565</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB96C08-41DE-4606-A0B5-398947B0D4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C8969C-BEC1-4B58-98F9-A655EB5D62AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Had regular classes and preparing for CA1 at home.</t>
+  </si>
+  <si>
+    <t>No regular classes. Studied and preparing for CA1 at home and relaxed.</t>
   </si>
 </sst>
 </file>
@@ -2149,27 +2152,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>420</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C8969C-BEC1-4B58-98F9-A655EB5D62AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CB9752-58E5-47D6-BE97-98692AB71AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,7 +267,7 @@
     <t>Had regular classes and preparing for CA1 at home.</t>
   </si>
   <si>
-    <t>No regular classes. Studied and preparing for CA1 at home and relaxed.</t>
+    <t>No regular classes. Preparing for CA1 at home and relaxed.</t>
   </si>
 </sst>
 </file>
@@ -2152,7 +2152,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>46270</v>
       </c>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANISH\OneDrive\Documents\GitHub\daily-routine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4CB9752-58E5-47D6-BE97-98692AB71AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A3BCA2-1E7A-4F25-B3A5-95BC27DF149D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2198,27 +2198,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B31" s="14">
+        <v>300</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>300</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>
